--- a/BackEnd/Ipsos/WebApi/Arquivos/ExcelExportacao/Modelos/Modelo_Exportação_Gráficos_Padrao_Filtro_Unico.xlsx
+++ b/BackEnd/Ipsos/WebApi/Arquivos/ExcelExportacao/Modelos/Modelo_Exportação_Gráficos_Padrao_Filtro_Unico.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithLatam\BHT_Globo\BHTGloboAuto\BackEnd\Ipsos\WebApi\Arquivos\ExcelExportacao\Modelos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithLatam\BHTEnlatados\BackEnd\Ipsos\WebApi\Arquivos\ExcelExportacao\Modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{789BC6F9-7A36-4F2D-8CA4-3F2B2BF364C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F700398B-93DB-4556-8259-13625F30E779}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29685" yWindow="780" windowWidth="20730" windowHeight="11160" tabRatio="326" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29685" yWindow="1230" windowWidth="20730" windowHeight="11160" tabRatio="326" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -967,60 +967,43 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>972155</xdr:colOff>
+      <xdr:colOff>863297</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>257024</xdr:rowOff>
+      <xdr:rowOff>311453</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2281475</xdr:colOff>
+      <xdr:colOff>2139487</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>638024</xdr:rowOff>
+      <xdr:rowOff>578120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Imagem 9">
+        <xdr:cNvPr id="13" name="Imagem 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9E032BF-0A1B-43E6-9363-34D0BB944459}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{522AB808-52BC-4B98-87A3-F2046942B7A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="1149048" y="257024"/>
-          <a:ext cx="1309320" cy="381000"/>
+          <a:off x="1040190" y="311453"/>
+          <a:ext cx="1276190" cy="266667"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
